--- a/sample-file.xlsx
+++ b/sample-file.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jadav\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dglig\Desktop\new motor od sample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A02226B-B59A-4CA2-994C-CD76B210213E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12433065-48F4-49E2-8772-8BD1EE8AE3BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{6C11E5AE-DA59-4038-8961-842537258FE7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6C11E5AE-DA59-4038-8961-842537258FE7}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="1" r:id="rId1"/>
@@ -21,24 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>Invoice Number</t>
   </si>
@@ -83,18 +71,6 @@
   </si>
   <si>
     <t>GST Amount</t>
-  </si>
-  <si>
-    <t>Metallic Parts</t>
-  </si>
-  <si>
-    <t>ABC</t>
-  </si>
-  <si>
-    <t>Bottom</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -535,39 +511,9 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>12354</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F2" s="2">
-        <v>50</v>
-      </c>
-      <c r="G2" s="2">
-        <v>18</v>
-      </c>
-      <c r="H2" s="2">
-        <v>1000</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="2">
-        <v>1852</v>
-      </c>
       <c r="K2" s="3">
         <f>ROUND((E2-(E2*F2/100))*(G2/100),2)</f>
-        <v>90</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
